--- a/input_data.xlsx
+++ b/input_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tarasgrendash/Library/CloudStorage/GoogleDrive-hrendash@globtalent.org/My Drive/Globtalent Web/map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF2BDCE4-63F9-3442-84A4-15B26CF28638}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42C90F1D-2D75-3745-83FA-5160FDDF0064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1520" yWindow="1480" windowWidth="28720" windowHeight="16860" xr2:uid="{F678B25C-8C70-49CD-BD59-1445232AE03B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="72">
   <si>
     <t>BIG students</t>
   </si>
@@ -237,6 +237,21 @@
   </si>
   <si>
     <t>Chile</t>
+  </si>
+  <si>
+    <t>Italy</t>
+  </si>
+  <si>
+    <t>Argentina</t>
+  </si>
+  <si>
+    <t>Ecuador</t>
+  </si>
+  <si>
+    <t>Cameroon</t>
+  </si>
+  <si>
+    <t>Sri Lanka</t>
   </si>
 </sst>
 </file>
@@ -906,7 +921,7 @@
         <v>42</v>
       </c>
       <c r="B19" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -937,31 +952,49 @@
       <c r="A23" t="s">
         <v>10</v>
       </c>
+      <c r="B23" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>38</v>
       </c>
+      <c r="B24" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>27</v>
       </c>
+      <c r="B25" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>13</v>
       </c>
+      <c r="B26" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>14</v>
       </c>
+      <c r="B27" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>58</v>
       </c>
+      <c r="B28" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
@@ -977,6 +1010,9 @@
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>60</v>
+      </c>
+      <c r="B30" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
